--- a/public/plantillas/12_PLAN_SERVICIO_EQUIPO.xlsx
+++ b/public/plantillas/12_PLAN_SERVICIO_EQUIPO.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ventura/Desktop/Programacion/recal-hse/public/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E0A6DD-A473-9D48-943D-78220CD1FCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147A58F8-7CCE-2645-954D-E2431A3D7A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3620" yWindow="0" windowWidth="29980" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MTTO DE MAQ" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'MTTO DE MAQ'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'MTTO DE MAQ'!$A$1:$K$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'MTTO DE MAQ'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>DESCRIPCIÓN</t>
   </si>
@@ -53,32 +53,6 @@
   </si>
   <si>
     <t>ELABORÓ</t>
-  </si>
-  <si>
-    <t>OSVALDO JIMENEZ MORALES</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">OBSERVACIONES:                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>-                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    -</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                                                                                     </t>
-    </r>
   </si>
   <si>
     <t>RECAL ESTRUCTURAS
@@ -106,10 +80,10 @@
     <t>AUTORIZÓ</t>
   </si>
   <si>
-    <t>ANTONIO SATURNO FRANCISCO RAMON</t>
+    <t>FECHA DE ÚLTIMO MANTENIMIENTO</t>
   </si>
   <si>
-    <t>FECHA DE ÚLTIMO MANTENIMIENTO</t>
+    <t xml:space="preserve">OBSERVACIONES: </t>
   </si>
 </sst>
 </file>
@@ -119,7 +93,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -176,12 +150,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -278,7 +246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -470,11 +438,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -484,23 +528,74 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="9" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,32 +639,23 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,7 +711,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_16_/+fKaBMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAEcIAAAAAAAAeAUAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAAAAAAAAAAACoAmgMAAAAAAgAAALYD5gCVAgAATQAAAMUVAACHBgAAAQAAADAAAAAUAAAAAAAAAAAA//8AAAEAAAD//wAAAQA="/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_16_/+fKaBMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAEcIAAAAAAAAeAUAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAAAAAAAAAAACoAmgMAAAAAAgAAALYD5gCVAgAATQAAAMUVAACHBgAAAQAAADAAAAAUAAAAAAAAAAAA//8AAAEAAAD//wAAAQA="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -919,7 +1005,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AE993"/>
+  <dimension ref="A1:AE994"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -933,75 +1019,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="94.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>10</v>
+      <c r="A1" s="28" t="s">
+        <v>8</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
     </row>
     <row r="2" spans="1:31" ht="45.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
-        <v>9</v>
+      <c r="A2" s="32" t="s">
+        <v>7</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="18"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="35"/>
     </row>
     <row r="3" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="22"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="39"/>
     </row>
     <row r="4" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="24"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="41"/>
     </row>
     <row r="5" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="26"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="43"/>
     </row>
     <row r="6" spans="1:31" ht="67.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
@@ -1020,22 +1106,22 @@
         <v>5</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="K6" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1091,20 +1177,18 @@
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
     </row>
-    <row r="8" spans="1:31" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
+    <row r="8" spans="1:31" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="17"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1126,22 +1210,20 @@
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
     </row>
-    <row r="9" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="30" t="s">
+    <row r="9" spans="1:31" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="32"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="21"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -1163,25 +1245,55 @@
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
     </row>
-    <row r="10" spans="1:31" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>7</v>
+    <row r="10" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="22"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23" t="s">
+        <v>6</v>
       </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="31" t="s">
-        <v>17</v>
+      <c r="E10" s="23"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="11" t="s">
+        <v>14</v>
       </c>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="35"/>
-    </row>
-    <row r="11" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="27"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+    </row>
+    <row r="11" spans="1:31" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="44"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="48"/>
     </row>
     <row r="12" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
@@ -4129,17 +4241,15 @@
     <row r="993" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2"/>
     </row>
+    <row r="994" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A994" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="4">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:F5"/>
     <mergeCell ref="G3:K5"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="G10:K10"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/plantillas/12_PLAN_SERVICIO_EQUIPO.xlsx
+++ b/public/plantillas/12_PLAN_SERVICIO_EQUIPO.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ventura/Desktop/Programacion/recal-hse/public/plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147A58F8-7CCE-2645-954D-E2431A3D7A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B4F4F6-DB24-C64F-9C3D-90FE93AAC597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="0" windowWidth="29980" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MTTO DE MAQ" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'MTTO DE MAQ'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'MTTO DE MAQ'!$A$1:$K$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'MTTO DE MAQ'!$1:$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -246,7 +246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -442,19 +442,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -518,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -549,35 +536,20 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -588,14 +560,29 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -638,24 +625,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,7 +680,7 @@
         <xdr:cNvPicPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_16_/+fKaBMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAEcIAAAAAAAAeAUAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAAAAAAAAAAACoAmgMAAAAAAgAAALYD5gCVAgAATQAAAMUVAACHBgAAAQAAADAAAAAUAAAAAAAAAAAA//8AAAEAAAD//wAAAQA="/>
+              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_16_/+fKaBMAAAAlAAAAEQAAAA0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAAAAAAAAAAAAAAAAAAPAAAAAQAAACMAAAAjAAAAIwAAAB4AAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAAAcAAAA4AAAAAAAAAAAAAAAAAAAA////AAAAAAAAAAAAAAAAAEcIAAAAAAAAeAUAAAAAAABkAAAAZAAAAAAAAAAjAAAABAAAAGQAAAAXAAAAFAAAAAAAAAAAAAAA/38AAP9/AAAAAAAACQAAAAQAAAAAAAAAHgAAAGgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABAnAAAQJwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAUAAAAAAAAAMDA/wAAAAAAZAAAADIAAAAAAAAAZAAAAAAAAAB/f38ACgAAACIAAAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAAAACQAAAAAAAAABwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAH9/fwAlAAAAWAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPwAAAAAAAACghgEAAAAAAAAAAAAAAAAADAAAAAEAAAAAAAAAAAAAAAAAAAAhAAAAMAAAACwAAAAAAAAAAAAAACoAmgMAAAAAAgAAALYD5gCVAgAATQAAAMUVAACHBgAAAQAAADAAAAAUAAAAAAAAAAAA//8AAAEAAAD//wAAAQA="/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1005,7 +974,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AE994"/>
+  <dimension ref="A1:AE993"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -1177,18 +1146,20 @@
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
     </row>
-    <row r="8" spans="1:31" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+    <row r="8" spans="1:31" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="B8" s="13"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="15"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1210,19 +1181,21 @@
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
     </row>
-    <row r="9" spans="1:31" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="18" t="s">
-        <v>16</v>
+    <row r="9" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17" t="s">
+        <v>6</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="20"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="18"/>
       <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="20"/>
       <c r="K9" s="21"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1245,55 +1218,21 @@
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
     </row>
-    <row r="10" spans="1:31" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
-      <c r="D10" s="23" t="s">
-        <v>6</v>
-      </c>
+      <c r="D10" s="23"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="26"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-    </row>
-    <row r="11" spans="1:31" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="48"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="26"/>
+    </row>
+    <row r="11" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
     </row>
     <row r="12" spans="1:31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
@@ -4240,9 +4179,6 @@
     </row>
     <row r="993" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2"/>
-    </row>
-    <row r="994" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A994" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
